--- a/new-stats/godoy-cruz.xlsx
+++ b/new-stats/godoy-cruz.xlsx
@@ -565,22 +565,58 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Def. de Belgrano</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
